--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55669-2023 artfynd.xlsx
+++ b/artfynd/A 55669-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136954543</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
